--- a/KatalonData/RADTestData/FEINmoreThan9Error.xlsx
+++ b/KatalonData/RADTestData/FEINmoreThan9Error.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cloned-Project-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{F94664B4-A075-48F0-96F3-FF1C8DDB6530}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{49EDB81C-00A4-43D0-9107-7F6B4E157577}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView windowHeight="16920" windowWidth="30960" xWindow="30600" xr2:uid="{597CD883-3A55-4BEE-94D3-336F4104083C}" yWindow="-120"/>
+    <workbookView windowHeight="16776" windowWidth="30936" xWindow="45972" xr2:uid="{597CD883-3A55-4BEE-94D3-336F4104083C}" yWindow="2952"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" r:id="rId1" sheetId="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="82">
   <si>
     <t>Result</t>
   </si>
@@ -107,343 +107,181 @@
     <t>Existing Liability with Notice/Invoice Number</t>
   </si>
   <si>
-    <t>Tue Jan 28 21:36:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:36:19 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:36:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:36:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:36:48 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:36:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:37:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:37:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:37:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:37:38 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:37:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:37:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:38:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:38:19 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:38:30 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:38:40 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:39:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:39:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:39:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:39:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:39:51 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:40:01 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:40:11 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:40:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:40:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 28 21:40:52 EST 2025</t>
-  </si>
-  <si>
     <t>Digital Advertising Gross Revenues</t>
   </si>
   <si>
+    <t>Thu May 14 16:23:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:23:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:24:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:24:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:24:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:24:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:24:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:24:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:25:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:25:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:25:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:25:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:25:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:25:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:25:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:26:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:26:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:26:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:26:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:26:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:26:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:26:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:27:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:27:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:27:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:27:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:27:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:27:48 EDT 2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Tue Feb 11 19:44:19 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:44:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:44:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:44:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:44:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:45:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:45:19 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:45:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:45:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:45:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:45:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:46:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:46:19 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:46:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:46:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:46:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:46:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:47:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:47:19 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:47:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:47:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:47:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:47:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:48:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:48:19 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:48:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:48:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Feb 11 19:48:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:58:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:00:12 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:01:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:02:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:03:51 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:05:04 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:06:17 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:07:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:07:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:07:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:08:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:08:14 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:08:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:09:38 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:10:50 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:12:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:13:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:13:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:13:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:13:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:14:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:14:11 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:14:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:14:33 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:14:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:14:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:15:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:16:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:25:43 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:26:54 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:28:04 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:29:14 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:30:25 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:31:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:32:46 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:33:57 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:34:03 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:34:09 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:34:15 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:34:21 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:34:26 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:35:37 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:36:47 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:37:57 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:39:07 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:39:13 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:39:19 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:39:25 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:39:31 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:39:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:39:42 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:39:48 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:39:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:39:59 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:40:04 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:41:17 EDT 2025</t>
+    <t>Thu May 21 22:45:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:45:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:45:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:45:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:45:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:45:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:46:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:46:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:46:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:46:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:46:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:46:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:47:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:47:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:47:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:47:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:47:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:47:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:47:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:48:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:48:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:48:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:48:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:48:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:48:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:49:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:49:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:49:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:49:32 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -814,18 +652,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5982E357-C335-4E2D-AD06-E7759BEC14C0}">
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.5703125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="17.5703125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="49.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="40.85546875" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.59765625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="17.59765625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="49.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="40.86328125" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -842,12 +680,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>53</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -859,12 +697,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -876,12 +714,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>55</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -893,12 +731,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
@@ -910,12 +748,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>57</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
@@ -927,12 +765,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
@@ -944,12 +782,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>5</v>
@@ -961,12 +799,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
@@ -978,12 +816,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>61</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
@@ -995,12 +833,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -1012,12 +850,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>5</v>
@@ -1029,12 +867,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>118</v>
+        <v>64</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>5</v>
@@ -1046,12 +884,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>5</v>
@@ -1063,12 +901,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
@@ -1080,12 +918,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>5</v>
@@ -1097,12 +935,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
@@ -1114,12 +952,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>5</v>
@@ -1131,12 +969,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
@@ -1148,12 +986,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
@@ -1165,12 +1003,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>5</v>
@@ -1182,12 +1020,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>127</v>
+        <v>73</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>5</v>
@@ -1199,12 +1037,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>5</v>
@@ -1216,12 +1054,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>5</v>
@@ -1233,12 +1071,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>5</v>
@@ -1250,12 +1088,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>5</v>
@@ -1267,12 +1105,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>5</v>
@@ -1284,12 +1122,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>133</v>
+        <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>5</v>
@@ -1298,15 +1136,15 @@
         <v>22</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>133</v>
+        <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>5</v>
@@ -1315,7 +1153,24 @@
         <v>8</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>49</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/KatalonData/RADTestData/FEINmoreThan9Error.xlsx
+++ b/KatalonData/RADTestData/FEINmoreThan9Error.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{49EDB81C-00A4-43D0-9107-7F6B4E157577}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464CD423-9E15-4FC8-85B6-A680B4DE39FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="16776" windowWidth="30936" xWindow="45972" xr2:uid="{597CD883-3A55-4BEE-94D3-336F4104083C}" yWindow="2952"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{597CD883-3A55-4BEE-94D3-336F4104083C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" r:id="rId1" sheetId="1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="85">
   <si>
     <t>Result</t>
   </si>
@@ -110,178 +110,187 @@
     <t>Digital Advertising Gross Revenues</t>
   </si>
   <si>
-    <t>Thu May 14 16:23:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:23:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:24:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:24:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:24:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:24:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:24:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:24:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:25:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:25:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:25:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:25:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:25:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:25:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:25:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:26:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:26:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:26:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:26:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:26:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:26:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:26:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:27:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:27:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:27:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:27:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:27:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:27:48 EDT 2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Thu May 21 22:45:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:45:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:45:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:45:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:45:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:45:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:46:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:46:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:46:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:46:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:46:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:46:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:47:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:47:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:47:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:47:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:47:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:47:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:47:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:48:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:48:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:48:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:48:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:48:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:48:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:49:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:49:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:49:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:49:32 EDT 2026</t>
+    <t>Wed Jun 24 23:54:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:54:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:54:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:54:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:55:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:55:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:55:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:55:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:55:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:55:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:55:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:56:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:56:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:56:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:56:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:56:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:56:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:56:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:57:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:57:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:57:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:57:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:57:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:57:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:58:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:58:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:58:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:58:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Motor Fuel Floor Tax</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 20:46:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 20:46:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:52:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:52:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:52:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:52:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:52:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:52:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:53:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:53:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:53:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:53:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:53:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:53:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:53:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:54:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:54:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:54:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:54:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:54:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:54:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:55:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:55:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:55:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:55:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:55:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:55:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:55:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:56:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:56:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:56:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:56:29 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -331,19 +340,19 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -360,10 +369,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -398,7 +407,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -450,7 +459,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -561,21 +570,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -592,7 +601,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -644,15 +653,15 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5982E357-C335-4E2D-AD06-E7759BEC14C0}">
-  <dimension ref="A1:F30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5982E357-C335-4E2D-AD06-E7759BEC14C0}">
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" style="1" width="9.1328125" collapsed="true"/>
@@ -681,11 +690,11 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>53</v>
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -698,11 +707,11 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>54</v>
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -715,11 +724,11 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>55</v>
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -732,11 +741,11 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>56</v>
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
@@ -749,11 +758,11 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>57</v>
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
@@ -766,11 +775,11 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>58</v>
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
@@ -783,11 +792,11 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>59</v>
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>5</v>
@@ -800,11 +809,11 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
-        <v>60</v>
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
@@ -817,11 +826,11 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
-        <v>61</v>
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
@@ -834,11 +843,11 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
-        <v>62</v>
+      <c r="A11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -851,11 +860,11 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
-        <v>63</v>
+      <c r="A12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>5</v>
@@ -868,11 +877,11 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" t="s">
-        <v>64</v>
+      <c r="A13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>5</v>
@@ -885,11 +894,11 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" t="s">
-        <v>65</v>
+      <c r="A14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>5</v>
@@ -902,11 +911,11 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" t="s">
-        <v>66</v>
+      <c r="A15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
@@ -919,11 +928,11 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" t="s">
-        <v>67</v>
+      <c r="A16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>5</v>
@@ -936,11 +945,11 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" t="s">
-        <v>68</v>
+      <c r="A17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
@@ -953,11 +962,11 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" t="s">
-        <v>69</v>
+      <c r="A18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>5</v>
@@ -970,11 +979,11 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" t="s">
-        <v>70</v>
+      <c r="A19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
@@ -987,11 +996,11 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" t="s">
-        <v>71</v>
+      <c r="A20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
@@ -1004,11 +1013,11 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" t="s">
-        <v>72</v>
+      <c r="A21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>5</v>
@@ -1021,11 +1030,11 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" t="s">
-        <v>73</v>
+      <c r="A22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>5</v>
@@ -1038,11 +1047,11 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" t="s">
-        <v>74</v>
+      <c r="A23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>5</v>
@@ -1055,11 +1064,11 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" t="s">
-        <v>75</v>
+      <c r="A24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>5</v>
@@ -1072,11 +1081,11 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" t="s">
-        <v>76</v>
+      <c r="A25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>5</v>
@@ -1089,11 +1098,11 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" t="s">
-        <v>77</v>
+      <c r="A26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>5</v>
@@ -1106,11 +1115,11 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" t="s">
-        <v>78</v>
+      <c r="A27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>5</v>
@@ -1123,11 +1132,11 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" t="s">
-        <v>79</v>
+      <c r="A28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>5</v>
@@ -1140,11 +1149,11 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" t="s">
-        <v>80</v>
+      <c r="A29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>5</v>
@@ -1157,11 +1166,11 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" t="s">
-        <v>81</v>
+      <c r="A30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>5</v>
@@ -1173,9 +1182,26 @@
         <v>23</v>
       </c>
     </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" t="s" s="1">
+        <v>84</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>

--- a/KatalonData/RADTestData/FEINmoreThan9Error.xlsx
+++ b/KatalonData/RADTestData/FEINmoreThan9Error.xlsx
@@ -3,21 +3,21 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464CD423-9E15-4FC8-85B6-A680B4DE39FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9FAE88-07A3-4254-B1F6-9BA72A11F9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{597CD883-3A55-4BEE-94D3-336F4104083C}"/>
+    <workbookView xWindow="5100" yWindow="1410" windowWidth="21600" windowHeight="11325" xr2:uid="{597CD883-3A55-4BEE-94D3-336F4104083C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="55">
   <si>
     <t>Result</t>
   </si>
@@ -110,97 +110,7 @@
     <t>Digital Advertising Gross Revenues</t>
   </si>
   <si>
-    <t>Wed Jun 24 23:54:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:54:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:54:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:54:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:55:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:55:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:55:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:55:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:55:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:55:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:55:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:56:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:56:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:56:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:56:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:56:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:56:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:56:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:57:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:57:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:57:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:57:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:57:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:57:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:58:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:58:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:58:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:58:34 EDT 2026</t>
-  </si>
-  <si>
     <t>Motor Fuel Floor Tax</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 20:46:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 20:46:44 EDT 2026</t>
   </si>
   <si>
     <t>Thu Jul 09 22:52:16 EDT 2026</t>
@@ -297,7 +207,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -664,12 +573,12 @@
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1328125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.59765625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="17.59765625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="49.1328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="40.86328125" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.1328125" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26.59765625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="17.59765625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="49.1328125" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="40.86328125" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.1328125" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -694,7 +603,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -711,7 +620,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -728,7 +637,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -745,7 +654,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
@@ -762,7 +671,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
@@ -779,7 +688,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
@@ -796,7 +705,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>5</v>
@@ -813,7 +722,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
@@ -830,7 +739,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
@@ -847,7 +756,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -864,7 +773,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>5</v>
@@ -881,7 +790,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>5</v>
@@ -898,7 +807,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>5</v>
@@ -915,7 +824,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
@@ -932,7 +841,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>5</v>
@@ -949,7 +858,7 @@
         <v>4</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
@@ -966,7 +875,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>5</v>
@@ -983,7 +892,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
@@ -1000,7 +909,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
@@ -1017,7 +926,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>5</v>
@@ -1034,7 +943,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>5</v>
@@ -1051,7 +960,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>5</v>
@@ -1068,7 +977,7 @@
         <v>4</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>5</v>
@@ -1085,7 +994,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>5</v>
@@ -1102,7 +1011,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>5</v>
@@ -1119,7 +1028,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>5</v>
@@ -1136,7 +1045,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>5</v>
@@ -1153,7 +1062,7 @@
         <v>4</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>5</v>
@@ -1170,7 +1079,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>5</v>
@@ -1186,8 +1095,8 @@
       <c r="A31" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B31" t="s" s="1">
-        <v>84</v>
+      <c r="B31" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>5</v>
@@ -1196,7 +1105,7 @@
         <v>8</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
